--- a/【1週間】最短で回路図を描けるようになるロードマップ.xlsx
+++ b/【1週間】最短で回路図を描けるようになるロードマップ.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/4e484cef2ba5051b/ドキュメント/000-個人資料/00-brexa/01-AutoCAD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="36" documentId="11_AD4D066CA252ABDACC1048D53991F55A73EEDF55" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C771709C-0FD5-4597-97BE-13CDA448446F}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="11_AD4D066CA252ABDACC1048D53991F55A73EEDF55" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01277047-E266-4F15-8795-B3B826AF4EF1}"/>
   <bookViews>
-    <workbookView xWindow="4070" yWindow="80" windowWidth="16200" windowHeight="11170" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32280" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="自己計画" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="初心者の手順" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="159">
   <si>
     <t>日付</t>
   </si>
@@ -273,12 +274,506 @@
   <si>
     <t>Enterで終了</t>
   </si>
+  <si>
+    <r>
+      <t>AutoCAD 2023 を初めて使うにあたり、</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>電気図面（電気設備図・制御盤・回路図）が主担当の場合に特に重要なポイント</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>を、初心者でもすぐ実務に役立つ形でまとめます。</t>
+    </r>
+  </si>
+  <si>
+    <t>「最初に確認すべきこと」「設定しておくと後でラクになること」「作図・修正のコツ」に分けて紹介します。</t>
+  </si>
+  <si>
+    <t>✅ 1. 最初に必ず確認すべきこと（会社内のルール・テンプレ）</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">まず Autodesk の操作より </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>社内ルールの把握が最優先</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> です。</t>
+    </r>
+  </si>
+  <si>
+    <t>以下チェックリストの項目を先輩や担当者に確認すると効率が上がります。</t>
+  </si>
+  <si>
+    <t>項目</t>
+  </si>
+  <si>
+    <t>内容</t>
+  </si>
+  <si>
+    <t>📌 図枠テンプレ（DWG）</t>
+  </si>
+  <si>
+    <t>A3/A2/A1など、社内で標準があるか</t>
+  </si>
+  <si>
+    <t>📌 レイヤ設定</t>
+  </si>
+  <si>
+    <t>色・線種・線幅・印刷スタイルのルール</t>
+  </si>
+  <si>
+    <t>📌 電気記号の標準</t>
+  </si>
+  <si>
+    <t>JIS/IEC？自社定義？ブロック化されているか</t>
+  </si>
+  <si>
+    <t>📌 文字スタイル</t>
+  </si>
+  <si>
+    <t>フォント、サイズ、横幅係数、寸法スタイル</t>
+  </si>
+  <si>
+    <t>📌 ケーブル・機器番号の表記</t>
+  </si>
+  <si>
+    <t>例：P-101／CB1／R-2 など番号体系</t>
+  </si>
+  <si>
+    <t>📌 シンボル配置の方向</t>
+  </si>
+  <si>
+    <t>縦書き？横書き？端子番号の記載位置</t>
+  </si>
+  <si>
+    <t>📌 外部参照（XREF）使用の有無</t>
+  </si>
+  <si>
+    <t>建築図・設備配置図の貼付ルール</t>
+  </si>
+  <si>
+    <t>📌 印刷方法</t>
+  </si>
+  <si>
+    <t>CTB（線幅） or STB（スタイル）?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">🔹 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>これを最初にそろえるほど後の作業がラクになり、書き直し防止に直結します。</t>
+    </r>
+  </si>
+  <si>
+    <t>⚙️ 2. 初期設定で必ず整えておくべき内容</t>
+  </si>
+  <si>
+    <t>AutoCAD 2023 で電気図面を扱う場合は以下を設定しておくと効率が大幅UPします。</t>
+  </si>
+  <si>
+    <t>🔸 Model/Layoutの理解</t>
+  </si>
+  <si>
+    <r>
+      <t>レイアウト側で印刷（PDF）する</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>のが一般的</t>
+    </r>
+  </si>
+  <si>
+    <t>→ Model空間は作図専用、Layoutは紙面（印刷）専用</t>
+  </si>
+  <si>
+    <t>🔸 単位とスケール</t>
+  </si>
+  <si>
+    <t>INSUNITS = mm（推奨）</t>
+  </si>
+  <si>
+    <t>注釈尺度の管理（1:50、1:100など）</t>
+  </si>
+  <si>
+    <t>🔸 レイヤ名の命名ルール例</t>
+  </si>
+  <si>
+    <t>用途</t>
+  </si>
+  <si>
+    <t>レイヤ名例</t>
+  </si>
+  <si>
+    <t>色</t>
+  </si>
+  <si>
+    <t>電力</t>
+  </si>
+  <si>
+    <t>PWR</t>
+  </si>
+  <si>
+    <t>照明</t>
+  </si>
+  <si>
+    <t>LGT</t>
+  </si>
+  <si>
+    <t>弱電</t>
+  </si>
+  <si>
+    <t>TEL</t>
+  </si>
+  <si>
+    <t>外形</t>
+  </si>
+  <si>
+    <t>FRAME</t>
+  </si>
+  <si>
+    <t>寸法・注釈</t>
+  </si>
+  <si>
+    <t>DIM / NOTE</t>
+  </si>
+  <si>
+    <t>➤ レイヤはできるだけ削除せずルールの統一を。</t>
+  </si>
+  <si>
+    <t>🔸 シンボル（ブロック管理）</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">電気記号を </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ブロック登録 + 属性</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> にすると管理が楽</t>
+    </r>
+  </si>
+  <si>
+    <t>例）ブレーカー、コンセント、照明、端子、PLC、リレーなど</t>
+  </si>
+  <si>
+    <t>✔ パラメトリックブロックが作れるとさらに効率UP</t>
+  </si>
+  <si>
+    <t>🧰 3. 作図・修正を早くする具体テクニック</t>
+  </si>
+  <si>
+    <t>初心者がすぐ効率UPできるものだけ厳選</t>
+  </si>
+  <si>
+    <t>🔹 オブジェクトスナップ（OSNAP）</t>
+  </si>
+  <si>
+    <t>端点・中点・交点・垂線・中心は常に ON</t>
+  </si>
+  <si>
+    <t>→ 電気図は接続精度が命</t>
+  </si>
+  <si>
+    <t>🔹 グリップ編集</t>
+  </si>
+  <si>
+    <t>配線の折れ点やシンボル位置調整が高速になる</t>
+  </si>
+  <si>
+    <t>（Stretch より早い場面多い）</t>
+  </si>
+  <si>
+    <t>🔹 Stretchコマンドの習得</t>
+  </si>
+  <si>
+    <t>範囲窓（左→右／右→左）で意味が変わる</t>
+  </si>
+  <si>
+    <t>配線・電路の延長に必須</t>
+  </si>
+  <si>
+    <t>🔹 ブロックの「属性編集（ATTEDIT）」</t>
+  </si>
+  <si>
+    <t>機器番号・回路番号を後から一括修正可能</t>
+  </si>
+  <si>
+    <t>🔹 配線の書き方ルール</t>
+  </si>
+  <si>
+    <t>ポリライン（PL）推奨</t>
+  </si>
+  <si>
+    <t>角度は 0°／90° 基本</t>
+  </si>
+  <si>
+    <t>垂直水平の整列は「整列(AL)」で高速化</t>
+  </si>
+  <si>
+    <t>🖨️ 4. PDF印刷（出図）時の注意</t>
+  </si>
+  <si>
+    <t>電気図の出図トラブルあるある</t>
+  </si>
+  <si>
+    <t>トラブル</t>
+  </si>
+  <si>
+    <t>原因</t>
+  </si>
+  <si>
+    <t>配線が細くて見えない</t>
+  </si>
+  <si>
+    <t>PLOTスタイル設定漏れ</t>
+  </si>
+  <si>
+    <t>文字が小さすぎる</t>
+  </si>
+  <si>
+    <t>注釈尺度不一致</t>
+  </si>
+  <si>
+    <t>枠が切れた</t>
+  </si>
+  <si>
+    <t>レイアウトのビューポート枠 overscan</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">→ 可能なら </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>社内で使われているPDF出力設定（PC3／CTB／STB）をコピー</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> してくるのが最速。</t>
+    </r>
+  </si>
+  <si>
+    <t>🔥 5. 電気図面で特にミスしやすい箇所</t>
+  </si>
+  <si>
+    <t>経験者がよく注意しているポイント</t>
+  </si>
+  <si>
+    <t>⚠ 記号の方向（上下左右）</t>
+  </si>
+  <si>
+    <t>端子番号やPLC入力の向きが逆だと重大ミス</t>
+  </si>
+  <si>
+    <t>⚠ 配線の「つながって見えるだけ」</t>
+  </si>
+  <si>
+    <r>
+      <t>端点が"接しているつもり"でも</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>実際は未接続</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>のケース</t>
+    </r>
+  </si>
+  <si>
+    <t>→ クロス点に「ノード（ドット）」を入れるルールがあるなら徹底</t>
+  </si>
+  <si>
+    <t>⚠ 番号の重複</t>
+  </si>
+  <si>
+    <t>盤番号</t>
+  </si>
+  <si>
+    <t>回路番号</t>
+  </si>
+  <si>
+    <t>機器番号</t>
+  </si>
+  <si>
+    <t>→ ルール化 or Excel管理で防止がおすすめ</t>
+  </si>
+  <si>
+    <t>⏩ 最後に — 習熟を一気に早める最短ロードマップ</t>
+  </si>
+  <si>
+    <t>段階</t>
+  </si>
+  <si>
+    <t>やること</t>
+  </si>
+  <si>
+    <t>①</t>
+  </si>
+  <si>
+    <t>社内テンプレ（図枠・レイヤ・シンボル・印刷設定）を収集</t>
+  </si>
+  <si>
+    <t>②</t>
+  </si>
+  <si>
+    <t>既存図面を2〜3枚開き「会社の作法」を把握</t>
+  </si>
+  <si>
+    <t>③</t>
+  </si>
+  <si>
+    <t>既存図の修正作業から開始（いきなり新規はNG）</t>
+  </si>
+  <si>
+    <t>④</t>
+  </si>
+  <si>
+    <t>よく使うブロック・コマンドのクイックアクセス登録</t>
+  </si>
+  <si>
+    <t>⑤</t>
+  </si>
+  <si>
+    <t>属性ブロックとレイヤ管理を覚えて高速作図へ</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>電気図は 1:1 が基本</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>です</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="6"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>が、建築図XREFに対し縮尺が重要</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -328,6 +823,40 @@
       <family val="3"/>
       <charset val="128"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color theme="1"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -364,16 +893,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -385,6 +911,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -684,7 +1223,7 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -698,9 +1237,9 @@
       <c r="C2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="4"/>
-    </row>
-    <row r="3" spans="1:4" ht="36">
+      <c r="D2" s="3"/>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -710,9 +1249,9 @@
       <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" ht="36">
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
@@ -722,11 +1261,11 @@
       <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="36">
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
@@ -736,11 +1275,11 @@
       <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="36">
+    <row r="6" spans="1:4">
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
@@ -750,11 +1289,11 @@
       <c r="C6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="36">
+    <row r="7" spans="1:4">
       <c r="A7" s="2" t="s">
         <v>17</v>
       </c>
@@ -764,9 +1303,9 @@
       <c r="C7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" ht="36">
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8" s="2" t="s">
         <v>20</v>
       </c>
@@ -776,7 +1315,7 @@
       <c r="C8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
@@ -798,37 +1337,37 @@
       </c>
     </row>
     <row r="2" spans="1:2" ht="38.5">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="22">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="6" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="6" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="6" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="6" t="s">
         <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="22">
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>35</v>
       </c>
     </row>
@@ -843,7 +1382,7 @@
       </c>
     </row>
     <row r="13" spans="1:2" ht="22">
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>38</v>
       </c>
     </row>
@@ -858,7 +1397,7 @@
       </c>
     </row>
     <row r="16" spans="1:2" ht="22">
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -878,37 +1417,37 @@
       </c>
     </row>
     <row r="20" spans="2:2" ht="38.5">
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="21" spans="2:2" ht="22">
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="22" spans="2:2">
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="6" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="23" spans="2:2">
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="6" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="24" spans="2:2">
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="6" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="25" spans="2:2">
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="6" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="22">
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="5" t="s">
         <v>51</v>
       </c>
     </row>
@@ -920,6 +1459,512 @@
     <row r="28" spans="2:2">
       <c r="B28" t="s">
         <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECBABC2C-B496-4E72-8D96-9B512F7CC64C}">
+  <dimension ref="A1:C105"/>
+  <sheetFormatPr defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="30.9140625" customWidth="1"/>
+    <col min="2" max="2" width="89.1640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="29">
+      <c r="A3" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="24.5" customHeight="1">
+      <c r="A7" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="31.5" customHeight="1">
+      <c r="A8" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="29" customHeight="1">
+      <c r="A9" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="24.5" customHeight="1">
+      <c r="A10" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="23" customHeight="1">
+      <c r="A11" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="19.5" customHeight="1">
+      <c r="A12" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="24" customHeight="1">
+      <c r="A13" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="21" customHeight="1">
+      <c r="A14" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="29">
+      <c r="A17" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="22">
+      <c r="A21" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" s="10" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="22">
+      <c r="A25" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" s="11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="6" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="22">
+      <c r="A30" s="5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="9" t="s">
+        <v>90</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="9">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="9" t="s">
+        <v>92</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="C34" s="9">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>97</v>
+      </c>
+      <c r="C35" s="9">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="12" customHeight="1">
+      <c r="A36" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="C36" s="9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="22">
+      <c r="A40" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="29">
+      <c r="A44" s="7" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="22">
+      <c r="A47" s="5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="22">
+      <c r="A51" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="22">
+      <c r="A55" s="5" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="22">
+      <c r="A59" s="5" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="22">
+      <c r="A63" s="5" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" s="6" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65" s="6" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="29">
+      <c r="A67" s="7" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="26" customHeight="1">
+      <c r="A72" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B72" s="9" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="15" customHeight="1">
+      <c r="A73" s="9" t="s">
+        <v>128</v>
+      </c>
+      <c r="B73" s="9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="20" customHeight="1">
+      <c r="A74" s="9" t="s">
+        <v>130</v>
+      </c>
+      <c r="B74" s="9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="29">
+      <c r="A78" s="7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="22">
+      <c r="A82" s="5" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="22">
+      <c r="A85" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" ht="22">
+      <c r="A89" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="6"/>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="6" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="6" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="6" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="29">
+      <c r="A98" s="7" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2">
+      <c r="A100" s="8" t="s">
+        <v>146</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="20" customHeight="1">
+      <c r="A101" s="9" t="s">
+        <v>148</v>
+      </c>
+      <c r="B101" s="9" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="18" customHeight="1">
+      <c r="A102" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="B102" s="9" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="22.5" customHeight="1">
+      <c r="A103" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B103" s="9" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="21" customHeight="1">
+      <c r="A104" s="9" t="s">
+        <v>154</v>
+      </c>
+      <c r="B104" s="9" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="12" customHeight="1">
+      <c r="A105" s="9" t="s">
+        <v>156</v>
+      </c>
+      <c r="B105" s="9" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>
